--- a/data/vessels/2026-10-25.xlsx
+++ b/data/vessels/2026-10-25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="455109" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B59049E-D7EB-49E6-B29D-9828CE64A946}"/>
+  <xr:revisionPtr revIDLastSave="455726" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8337A213-C19A-45D5-B15A-7BFC60D00B88}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -341,7 +341,7 @@
     <t>NORTH STAR</t>
   </si>
   <si>
-    <t>Waiting 3.5 days</t>
+    <t>Waiting 3.7 days</t>
   </si>
   <si>
     <t>EB Service 2</t>
@@ -554,15 +554,15 @@
     <t>LOTUS A</t>
   </si>
   <si>
+    <t>SWIFT ACE</t>
+  </si>
+  <si>
+    <t>152A</t>
+  </si>
+  <si>
     <t>GLOVIS TRUST</t>
   </si>
   <si>
-    <t>SWIFT ACE</t>
-  </si>
-  <si>
-    <t>152A</t>
-  </si>
-  <si>
     <t>ONE MODERN</t>
   </si>
   <si>
@@ -689,16 +689,16 @@
     <t>499-144E</t>
   </si>
   <si>
+    <t>BERGAMOT ACE</t>
+  </si>
+  <si>
+    <t>159A</t>
+  </si>
+  <si>
     <t>GLOVIS SUMMIT</t>
   </si>
   <si>
     <t>APS Stevedoring</t>
-  </si>
-  <si>
-    <t>BERGAMOT ACE</t>
-  </si>
-  <si>
-    <t>159A</t>
   </si>
   <si>
     <t>MSC ELISABETTA</t>
@@ -3245,20 +3245,14 @@
         <v>70</v>
       </c>
       <c r="C61" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="D61" t="s">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="F61" t="s">
         <v>73</v>
       </c>
-      <c r="G61" t="s">
-        <v>73</v>
-      </c>
-      <c r="H61" t="s">
-        <v>74</v>
-      </c>
       <c r="I61" t="s">
         <v>19</v>
       </c>
@@ -3266,7 +3260,7 @@
         <v>46332.291666666664</v>
       </c>
       <c r="K61" s="2">
-        <v>46333.125</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L61" t="s">
         <v>24</v>
@@ -3280,14 +3274,20 @@
         <v>70</v>
       </c>
       <c r="C62" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="D62" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="F62" t="s">
         <v>73</v>
       </c>
+      <c r="G62" t="s">
+        <v>73</v>
+      </c>
+      <c r="H62" t="s">
+        <v>74</v>
+      </c>
       <c r="I62" t="s">
         <v>19</v>
       </c>
@@ -3295,7 +3295,7 @@
         <v>46332.291666666664</v>
       </c>
       <c r="K62" s="2">
-        <v>46332.791666666664</v>
+        <v>46333.125</v>
       </c>
       <c r="L62" t="s">
         <v>24</v>
@@ -3561,11 +3561,11 @@
       <c r="D71" t="s">
         <v>171</v>
       </c>
-      <c r="E71" s="1">
-        <v>11</v>
+      <c r="E71" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="F71" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="G71" t="s">
         <v>18</v>
@@ -3594,13 +3594,13 @@
         <v>31</v>
       </c>
       <c r="D72" t="s">
-        <v>172</v>
-      </c>
-      <c r="E72" s="1" t="s">
         <v>173</v>
       </c>
+      <c r="E72" s="1">
+        <v>11</v>
+      </c>
       <c r="F72" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="G72" t="s">
         <v>18</v>
@@ -3629,10 +3629,10 @@
         <v>31</v>
       </c>
       <c r="D73" t="s">
+        <v>171</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="F73" t="s">
         <v>86</v>
@@ -3789,22 +3789,19 @@
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="C78" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="D78" t="s">
-        <v>179</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>180</v>
+        <v>92</v>
       </c>
       <c r="F78" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="I78" t="s">
         <v>19</v>
@@ -3813,7 +3810,7 @@
         <v>46337.333333333336</v>
       </c>
       <c r="K78" s="2">
-        <v>46339.333333333336</v>
+        <v>46337.833333333336</v>
       </c>
       <c r="L78" t="s">
         <v>24</v>
@@ -3821,19 +3818,22 @@
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B79" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="C79" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="D79" t="s">
-        <v>92</v>
+        <v>179</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>180</v>
       </c>
       <c r="F79" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="I79" t="s">
         <v>19</v>
@@ -3842,7 +3842,7 @@
         <v>46337.333333333336</v>
       </c>
       <c r="K79" s="2">
-        <v>46337.833333333336</v>
+        <v>46339.333333333336</v>
       </c>
       <c r="L79" t="s">
         <v>24</v>
@@ -4757,18 +4757,15 @@
       <c r="D108" t="s">
         <v>216</v>
       </c>
-      <c r="E108" s="1">
-        <v>89</v>
+      <c r="E108" s="1" t="s">
+        <v>217</v>
       </c>
       <c r="F108" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="G108" t="s">
         <v>18</v>
       </c>
-      <c r="H108" t="s">
-        <v>217</v>
-      </c>
       <c r="I108" t="s">
         <v>34</v>
       </c>
@@ -4795,14 +4792,17 @@
       <c r="D109" t="s">
         <v>218</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>219</v>
+      <c r="E109" s="1">
+        <v>89</v>
       </c>
       <c r="F109" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="G109" t="s">
         <v>18</v>
+      </c>
+      <c r="H109" t="s">
+        <v>219</v>
       </c>
       <c r="I109" t="s">
         <v>34</v>
@@ -5076,12 +5076,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
   <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
   <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
@@ -5089,7 +5083,7 @@
 </scriptIds>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -5098,7 +5092,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -5236,18 +5230,24 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
--- a/data/vessels/2026-10-25.xlsx
+++ b/data/vessels/2026-10-25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="455726" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8337A213-C19A-45D5-B15A-7BFC60D00B88}"/>
+  <xr:revisionPtr revIDLastSave="456099" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA1A42B7-B898-42AB-91AE-456C6A1005C9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -170,6 +170,18 @@
     <t>COSCO SHIPPING LINES</t>
   </si>
   <si>
+    <t>CPNW</t>
+  </si>
+  <si>
+    <t>CMA CGM FORT JAMES</t>
+  </si>
+  <si>
+    <t>CPN04/CPN05</t>
+  </si>
+  <si>
+    <t>CMA CGM</t>
+  </si>
+  <si>
     <t>PN1</t>
   </si>
   <si>
@@ -179,18 +191,6 @@
     <t>198E</t>
   </si>
   <si>
-    <t>CPNW</t>
-  </si>
-  <si>
-    <t>CMA CGM FORT JAMES</t>
-  </si>
-  <si>
-    <t>CPN04/CPN05</t>
-  </si>
-  <si>
-    <t>CMA CGM</t>
-  </si>
-  <si>
     <t>T7</t>
   </si>
   <si>
@@ -233,24 +233,24 @@
     <t>640E/643W</t>
   </si>
   <si>
+    <t>LIBERTY PEACE</t>
+  </si>
+  <si>
+    <t>086S</t>
+  </si>
+  <si>
+    <t>Liberty</t>
+  </si>
+  <si>
+    <t>Pacific Terminals</t>
+  </si>
+  <si>
     <t>Blair</t>
   </si>
   <si>
     <t>LIBERTY PASSION</t>
   </si>
   <si>
-    <t>Liberty</t>
-  </si>
-  <si>
-    <t>Pacific Terminals</t>
-  </si>
-  <si>
-    <t>LIBERTY PEACE</t>
-  </si>
-  <si>
-    <t>086S</t>
-  </si>
-  <si>
     <t>WST</t>
   </si>
   <si>
@@ -341,7 +341,7 @@
     <t>NORTH STAR</t>
   </si>
   <si>
-    <t>Waiting 3.7 days</t>
+    <t>Waiting 3.9 days</t>
   </si>
   <si>
     <t>EB Service 2</t>
@@ -515,15 +515,15 @@
     <t>KW665</t>
   </si>
   <si>
+    <t>MAUNAWILI</t>
+  </si>
+  <si>
     <t>MSC YUKTA X</t>
   </si>
   <si>
     <t>UK644R</t>
   </si>
   <si>
-    <t>MAUNAWILI</t>
-  </si>
-  <si>
     <t>SM MUMBAI</t>
   </si>
   <si>
@@ -554,13 +554,13 @@
     <t>LOTUS A</t>
   </si>
   <si>
+    <t>GLOVIS TRUST</t>
+  </si>
+  <si>
     <t>SWIFT ACE</t>
   </si>
   <si>
     <t>152A</t>
-  </si>
-  <si>
-    <t>GLOVIS TRUST</t>
   </si>
   <si>
     <t>ONE MODERN</t>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
         <v>43</v>
@@ -1414,10 +1414,10 @@
         <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="G8" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I8" t="s">
         <v>19</v>
@@ -1426,7 +1426,7 @@
         <v>46321.25</v>
       </c>
       <c r="K8" s="2">
-        <v>46323.166666666664</v>
+        <v>46322.75</v>
       </c>
       <c r="L8" t="s">
         <v>24</v>
@@ -1434,25 +1434,25 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="I9" t="s">
         <v>19</v>
@@ -1461,7 +1461,7 @@
         <v>46321.25</v>
       </c>
       <c r="K9" s="2">
-        <v>46322.75</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L9" t="s">
         <v>24</v>
@@ -1580,12 +1580,15 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
       </c>
       <c r="D13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F13" t="s">
@@ -1604,7 +1607,7 @@
         <v>46322.791666666664</v>
       </c>
       <c r="K13" s="2">
-        <v>46323.75</v>
+        <v>46325.770833333336</v>
       </c>
       <c r="L13" t="s">
         <v>35</v>
@@ -1615,15 +1618,12 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="1" t="s">
         <v>69</v>
       </c>
       <c r="F14" t="s">
@@ -1642,7 +1642,7 @@
         <v>46322.791666666664</v>
       </c>
       <c r="K14" s="2">
-        <v>46325.770833333336</v>
+        <v>46323.75</v>
       </c>
       <c r="L14" t="s">
         <v>35</v>
@@ -1808,7 +1808,7 @@
         <v>89</v>
       </c>
       <c r="F19" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
         <v>18</v>
@@ -1869,7 +1869,7 @@
         <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
         <v>31</v>
@@ -2146,7 +2146,7 @@
         <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
         <v>31</v>
@@ -2184,7 +2184,7 @@
         <v>37</v>
       </c>
       <c r="C30" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D30" t="s">
         <v>108</v>
@@ -2193,7 +2193,7 @@
         <v>109</v>
       </c>
       <c r="F30" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G30" t="s">
         <v>18</v>
@@ -2216,7 +2216,7 @@
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C31" t="s">
         <v>31</v>
@@ -2636,7 +2636,7 @@
         <v>25</v>
       </c>
       <c r="C43" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D43" t="s">
         <v>136</v>
@@ -2907,7 +2907,7 @@
         <v>25</v>
       </c>
       <c r="C51" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D51" t="s">
         <v>149</v>
@@ -2939,7 +2939,7 @@
         <v>25</v>
       </c>
       <c r="C52" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D52" t="s">
         <v>149</v>
@@ -2968,7 +2968,7 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C53" t="s">
         <v>31</v>
@@ -3003,7 +3003,7 @@
         <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C54" t="s">
         <v>31</v>
@@ -3169,25 +3169,25 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="C59" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="D59" t="s">
         <v>158</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="F59" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="G59" t="s">
-        <v>18</v>
+        <v>73</v>
+      </c>
+      <c r="H59" t="s">
+        <v>74</v>
       </c>
       <c r="I59" t="s">
         <v>19</v>
@@ -3196,7 +3196,7 @@
         <v>46332.291666666664</v>
       </c>
       <c r="K59" s="2">
-        <v>46334.166666666664</v>
+        <v>46333.125</v>
       </c>
       <c r="L59" t="s">
         <v>24</v>
@@ -3204,25 +3204,19 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="C60" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="D60" t="s">
-        <v>158</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="F60" t="s">
-        <v>117</v>
-      </c>
-      <c r="G60" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="I60" t="s">
         <v>19</v>
@@ -3231,7 +3225,7 @@
         <v>46332.291666666664</v>
       </c>
       <c r="K60" s="2">
-        <v>46334.166666666664</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L60" t="s">
         <v>24</v>
@@ -3239,19 +3233,25 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B61" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="C61" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="D61" t="s">
-        <v>72</v>
+        <v>159</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="F61" t="s">
-        <v>73</v>
+        <v>117</v>
+      </c>
+      <c r="G61" t="s">
+        <v>18</v>
       </c>
       <c r="I61" t="s">
         <v>19</v>
@@ -3260,7 +3260,7 @@
         <v>46332.291666666664</v>
       </c>
       <c r="K61" s="2">
-        <v>46332.791666666664</v>
+        <v>46334.166666666664</v>
       </c>
       <c r="L61" t="s">
         <v>24</v>
@@ -3268,25 +3268,25 @@
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B62" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="C62" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="D62" t="s">
+        <v>159</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>160</v>
       </c>
       <c r="F62" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="G62" t="s">
-        <v>73</v>
-      </c>
-      <c r="H62" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="I62" t="s">
         <v>19</v>
@@ -3295,7 +3295,7 @@
         <v>46332.291666666664</v>
       </c>
       <c r="K62" s="2">
-        <v>46333.125</v>
+        <v>46334.166666666664</v>
       </c>
       <c r="L62" t="s">
         <v>24</v>
@@ -3387,7 +3387,7 @@
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C66" t="s">
         <v>31</v>
@@ -3524,7 +3524,7 @@
         <v>37</v>
       </c>
       <c r="C70" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D70" t="s">
         <v>170</v>
@@ -3533,7 +3533,7 @@
         <v>94</v>
       </c>
       <c r="F70" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I70" t="s">
         <v>19</v>
@@ -3561,11 +3561,11 @@
       <c r="D71" t="s">
         <v>171</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>172</v>
+      <c r="E71" s="1">
+        <v>11</v>
       </c>
       <c r="F71" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="G71" t="s">
         <v>18</v>
@@ -3594,13 +3594,13 @@
         <v>31</v>
       </c>
       <c r="D72" t="s">
+        <v>172</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="E72" s="1">
-        <v>11</v>
-      </c>
       <c r="F72" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="G72" t="s">
         <v>18</v>
@@ -3623,16 +3623,16 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C73" t="s">
         <v>31</v>
       </c>
       <c r="D73" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F73" t="s">
         <v>86</v>
@@ -3690,7 +3690,7 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C75" t="s">
         <v>31</v>
@@ -3882,7 +3882,7 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C81" t="s">
         <v>31</v>
@@ -3981,7 +3981,7 @@
         <v>25</v>
       </c>
       <c r="C84" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D84" t="s">
         <v>186</v>
@@ -4013,7 +4013,7 @@
         <v>25</v>
       </c>
       <c r="C85" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D85" t="s">
         <v>186</v>
@@ -4295,7 +4295,7 @@
         <v>37</v>
       </c>
       <c r="C94" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D94" t="s">
         <v>196</v>
@@ -4304,7 +4304,7 @@
         <v>57</v>
       </c>
       <c r="F94" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I94" t="s">
         <v>19</v>
@@ -4420,7 +4420,7 @@
         <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C98" t="s">
         <v>31</v>
@@ -4490,7 +4490,7 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C100" t="s">
         <v>31</v>
@@ -4592,7 +4592,7 @@
         <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C103" t="s">
         <v>31</v>

--- a/data/vessels/2026-10-25.xlsx
+++ b/data/vessels/2026-10-25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="456099" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA1A42B7-B898-42AB-91AE-456C6A1005C9}"/>
+  <xr:revisionPtr revIDLastSave="456346" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36961B31-8301-457A-9E9E-8F1D8FC13D29}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -302,6 +302,12 @@
     <t>ONE</t>
   </si>
   <si>
+    <t>ONE DURBAN</t>
+  </si>
+  <si>
+    <t>PN32639E</t>
+  </si>
+  <si>
     <t>Oceania</t>
   </si>
   <si>
@@ -311,12 +317,6 @@
     <t>0Y1N2/0T1N3</t>
   </si>
   <si>
-    <t>ONE DURBAN</t>
-  </si>
-  <si>
-    <t>PN32639E</t>
-  </si>
-  <si>
     <t>MATSON ANCHORAGE</t>
   </si>
   <si>
@@ -341,7 +341,7 @@
     <t>NORTH STAR</t>
   </si>
   <si>
-    <t>Waiting 3.9 days</t>
+    <t>Waiting 4 days</t>
   </si>
   <si>
     <t>EB Service 2</t>
@@ -515,15 +515,15 @@
     <t>KW665</t>
   </si>
   <si>
+    <t>MSC YUKTA X</t>
+  </si>
+  <si>
+    <t>UK644R</t>
+  </si>
+  <si>
     <t>MAUNAWILI</t>
   </si>
   <si>
-    <t>MSC YUKTA X</t>
-  </si>
-  <si>
-    <t>UK644R</t>
-  </si>
-  <si>
     <t>SM MUMBAI</t>
   </si>
   <si>
@@ -554,15 +554,15 @@
     <t>LOTUS A</t>
   </si>
   <si>
+    <t>SWIFT ACE</t>
+  </si>
+  <si>
+    <t>152A</t>
+  </si>
+  <si>
     <t>GLOVIS TRUST</t>
   </si>
   <si>
-    <t>SWIFT ACE</t>
-  </si>
-  <si>
-    <t>152A</t>
-  </si>
-  <si>
     <t>ONE MODERN</t>
   </si>
   <si>
@@ -650,18 +650,18 @@
     <t>1476-009E</t>
   </si>
   <si>
+    <t>EUPHONY ACE</t>
+  </si>
+  <si>
+    <t>166A</t>
+  </si>
+  <si>
     <t>TOURMALINE ACE</t>
   </si>
   <si>
     <t>013A</t>
   </si>
   <si>
-    <t>EUPHONY ACE</t>
-  </si>
-  <si>
-    <t>166A</t>
-  </si>
-  <si>
     <t>MAERSK SARNIA</t>
   </si>
   <si>
@@ -689,16 +689,16 @@
     <t>499-144E</t>
   </si>
   <si>
+    <t>GLOVIS SUMMIT</t>
+  </si>
+  <si>
+    <t>APS Stevedoring</t>
+  </si>
+  <si>
     <t>BERGAMOT ACE</t>
   </si>
   <si>
     <t>159A</t>
-  </si>
-  <si>
-    <t>GLOVIS SUMMIT</t>
-  </si>
-  <si>
-    <t>APS Stevedoring</t>
   </si>
   <si>
     <t>MSC ELISABETTA</t>
@@ -1793,29 +1793,26 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" t="s">
         <v>87</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="G19" t="s">
         <v>18</v>
       </c>
-      <c r="H19" t="s">
-        <v>74</v>
-      </c>
       <c r="I19" t="s">
         <v>19</v>
       </c>
@@ -1823,7 +1820,7 @@
         <v>46324.25</v>
       </c>
       <c r="K19" s="2">
-        <v>46325.166666666664</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="L19" t="s">
         <v>24</v>
@@ -1831,13 +1828,13 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s">
         <v>90</v>
@@ -1846,11 +1843,14 @@
         <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="G20" t="s">
         <v>18</v>
       </c>
+      <c r="H20" t="s">
+        <v>74</v>
+      </c>
       <c r="I20" t="s">
         <v>19</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>46324.25</v>
       </c>
       <c r="K20" s="2">
-        <v>46326.166666666664</v>
+        <v>46325.166666666664</v>
       </c>
       <c r="L20" t="s">
         <v>24</v>
@@ -3169,25 +3169,25 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B59" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="C59" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="D59" t="s">
         <v>158</v>
       </c>
+      <c r="E59" s="1" t="s">
+        <v>159</v>
+      </c>
       <c r="F59" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="G59" t="s">
-        <v>73</v>
-      </c>
-      <c r="H59" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="I59" t="s">
         <v>19</v>
@@ -3196,7 +3196,7 @@
         <v>46332.291666666664</v>
       </c>
       <c r="K59" s="2">
-        <v>46333.125</v>
+        <v>46334.166666666664</v>
       </c>
       <c r="L59" t="s">
         <v>24</v>
@@ -3233,25 +3233,25 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="C61" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="D61" t="s">
-        <v>159</v>
-      </c>
-      <c r="E61" s="1" t="s">
         <v>160</v>
       </c>
       <c r="F61" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="G61" t="s">
-        <v>18</v>
+        <v>73</v>
+      </c>
+      <c r="H61" t="s">
+        <v>74</v>
       </c>
       <c r="I61" t="s">
         <v>19</v>
@@ -3260,7 +3260,7 @@
         <v>46332.291666666664</v>
       </c>
       <c r="K61" s="2">
-        <v>46334.166666666664</v>
+        <v>46333.125</v>
       </c>
       <c r="L61" t="s">
         <v>24</v>
@@ -3277,10 +3277,10 @@
         <v>118</v>
       </c>
       <c r="D62" t="s">
+        <v>158</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="F62" t="s">
         <v>117</v>
@@ -3561,11 +3561,11 @@
       <c r="D71" t="s">
         <v>171</v>
       </c>
-      <c r="E71" s="1">
-        <v>11</v>
+      <c r="E71" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="F71" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="G71" t="s">
         <v>18</v>
@@ -3594,13 +3594,13 @@
         <v>31</v>
       </c>
       <c r="D72" t="s">
-        <v>172</v>
-      </c>
-      <c r="E72" s="1" t="s">
         <v>173</v>
       </c>
+      <c r="E72" s="1">
+        <v>11</v>
+      </c>
       <c r="F72" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="G72" t="s">
         <v>18</v>
@@ -3629,10 +3629,10 @@
         <v>31</v>
       </c>
       <c r="D73" t="s">
+        <v>171</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="F73" t="s">
         <v>86</v>
@@ -4455,7 +4455,7 @@
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="C99" t="s">
         <v>31</v>
@@ -4472,6 +4472,9 @@
       <c r="G99" t="s">
         <v>18</v>
       </c>
+      <c r="H99" t="s">
+        <v>74</v>
+      </c>
       <c r="I99" t="s">
         <v>34</v>
       </c>
@@ -4490,7 +4493,7 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C100" t="s">
         <v>31</v>
@@ -4507,9 +4510,6 @@
       <c r="G100" t="s">
         <v>18</v>
       </c>
-      <c r="H100" t="s">
-        <v>74</v>
-      </c>
       <c r="I100" t="s">
         <v>34</v>
       </c>
@@ -4598,10 +4598,10 @@
         <v>31</v>
       </c>
       <c r="D103" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F103" t="s">
         <v>86</v>
@@ -4757,15 +4757,18 @@
       <c r="D108" t="s">
         <v>216</v>
       </c>
-      <c r="E108" s="1" t="s">
-        <v>217</v>
+      <c r="E108" s="1">
+        <v>89</v>
       </c>
       <c r="F108" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="G108" t="s">
         <v>18</v>
       </c>
+      <c r="H108" t="s">
+        <v>217</v>
+      </c>
       <c r="I108" t="s">
         <v>34</v>
       </c>
@@ -4792,17 +4795,14 @@
       <c r="D109" t="s">
         <v>218</v>
       </c>
-      <c r="E109" s="1">
-        <v>89</v>
+      <c r="E109" s="1" t="s">
+        <v>219</v>
       </c>
       <c r="F109" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="G109" t="s">
         <v>18</v>
-      </c>
-      <c r="H109" t="s">
-        <v>219</v>
       </c>
       <c r="I109" t="s">
         <v>34</v>
@@ -5011,7 +5011,7 @@
         <v>37</v>
       </c>
       <c r="C116" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D116" t="s">
         <v>226</v>
@@ -5043,7 +5043,7 @@
         <v>37</v>
       </c>
       <c r="C117" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D117" t="s">
         <v>226</v>
@@ -5076,6 +5076,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
   <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
   <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
@@ -5083,7 +5089,7 @@
 </scriptIds>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -5092,7 +5098,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -5230,24 +5236,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
--- a/data/vessels/2026-10-25.xlsx
+++ b/data/vessels/2026-10-25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="456346" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36961B31-8301-457A-9E9E-8F1D8FC13D29}"/>
+  <xr:revisionPtr revIDLastSave="456725" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94C83293-58A5-4D83-915F-57E041F4C8A2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="227">
   <si>
     <t>Harbor</t>
   </si>
@@ -302,21 +302,21 @@
     <t>ONE</t>
   </si>
   <si>
+    <t>Oceania</t>
+  </si>
+  <si>
+    <t>CMA CGM DUTCH HARBOR</t>
+  </si>
+  <si>
+    <t>0Y1N2/0T1N3</t>
+  </si>
+  <si>
     <t>ONE DURBAN</t>
   </si>
   <si>
     <t>PN32639E</t>
   </si>
   <si>
-    <t>Oceania</t>
-  </si>
-  <si>
-    <t>CMA CGM DUTCH HARBOR</t>
-  </si>
-  <si>
-    <t>0Y1N2/0T1N3</t>
-  </si>
-  <si>
     <t>MATSON ANCHORAGE</t>
   </si>
   <si>
@@ -341,9 +341,6 @@
     <t>NORTH STAR</t>
   </si>
   <si>
-    <t>Waiting 4 days</t>
-  </si>
-  <si>
     <t>EB Service 2</t>
   </si>
   <si>
@@ -467,21 +464,21 @@
     <t>MC644R</t>
   </si>
   <si>
+    <t>TONGALA</t>
+  </si>
+  <si>
+    <t>KW666</t>
+  </si>
+  <si>
+    <t>Wallenius</t>
+  </si>
+  <si>
+    <t>Jones Stevedoring Co</t>
+  </si>
+  <si>
     <t>GLOVIS TREASURE</t>
   </si>
   <si>
-    <t>TONGALA</t>
-  </si>
-  <si>
-    <t>KW666</t>
-  </si>
-  <si>
-    <t>Wallenius</t>
-  </si>
-  <si>
-    <t>Jones Stevedoring Co</t>
-  </si>
-  <si>
     <t>MSC SABRINA</t>
   </si>
   <si>
@@ -515,15 +512,15 @@
     <t>KW665</t>
   </si>
   <si>
+    <t>MAUNAWILI</t>
+  </si>
+  <si>
     <t>MSC YUKTA X</t>
   </si>
   <si>
     <t>UK644R</t>
   </si>
   <si>
-    <t>MAUNAWILI</t>
-  </si>
-  <si>
     <t>SM MUMBAI</t>
   </si>
   <si>
@@ -650,18 +647,18 @@
     <t>1476-009E</t>
   </si>
   <si>
+    <t>TOURMALINE ACE</t>
+  </si>
+  <si>
+    <t>013A</t>
+  </si>
+  <si>
     <t>EUPHONY ACE</t>
   </si>
   <si>
     <t>166A</t>
   </si>
   <si>
-    <t>TOURMALINE ACE</t>
-  </si>
-  <si>
-    <t>013A</t>
-  </si>
-  <si>
     <t>MAERSK SARNIA</t>
   </si>
   <si>
@@ -689,16 +686,16 @@
     <t>499-144E</t>
   </si>
   <si>
+    <t>BERGAMOT ACE</t>
+  </si>
+  <si>
+    <t>159A</t>
+  </si>
+  <si>
     <t>GLOVIS SUMMIT</t>
   </si>
   <si>
     <t>APS Stevedoring</t>
-  </si>
-  <si>
-    <t>BERGAMOT ACE</t>
-  </si>
-  <si>
-    <t>159A</t>
   </si>
   <si>
     <t>MSC ELISABETTA</t>
@@ -1793,26 +1790,29 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F19" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
         <v>18</v>
       </c>
+      <c r="H19" t="s">
+        <v>74</v>
+      </c>
       <c r="I19" t="s">
         <v>19</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>46324.25</v>
       </c>
       <c r="K19" s="2">
-        <v>46326.166666666664</v>
+        <v>46325.166666666664</v>
       </c>
       <c r="L19" t="s">
         <v>24</v>
@@ -1828,13 +1828,13 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="D20" t="s">
         <v>90</v>
@@ -1843,14 +1843,11 @@
         <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="G20" t="s">
         <v>18</v>
       </c>
-      <c r="H20" t="s">
-        <v>74</v>
-      </c>
       <c r="I20" t="s">
         <v>19</v>
       </c>
@@ -1858,7 +1855,7 @@
         <v>46324.25</v>
       </c>
       <c r="K20" s="2">
-        <v>46325.166666666664</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="L20" t="s">
         <v>24</v>
@@ -2101,9 +2098,6 @@
       </c>
       <c r="K27" s="2">
         <v>46326.041666666664</v>
-      </c>
-      <c r="L27" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -2114,19 +2108,19 @@
         <v>37</v>
       </c>
       <c r="C28" t="s">
+        <v>100</v>
+      </c>
+      <c r="D28" t="s">
         <v>101</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="F28" t="s">
         <v>103</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>104</v>
-      </c>
-      <c r="G28" t="s">
-        <v>105</v>
       </c>
       <c r="I28" t="s">
         <v>19</v>
@@ -2152,10 +2146,10 @@
         <v>31</v>
       </c>
       <c r="D29" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="F29" t="s">
         <v>86</v>
@@ -2187,10 +2181,10 @@
         <v>43</v>
       </c>
       <c r="D30" t="s">
+        <v>107</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="F30" t="s">
         <v>46</v>
@@ -2222,10 +2216,10 @@
         <v>31</v>
       </c>
       <c r="D31" t="s">
+        <v>109</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="F31" t="s">
         <v>86</v>
@@ -2257,7 +2251,7 @@
         <v>21</v>
       </c>
       <c r="D32" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
@@ -2286,19 +2280,19 @@
         <v>36</v>
       </c>
       <c r="B33" t="s">
+        <v>112</v>
+      </c>
+      <c r="C33" t="s">
         <v>113</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>114</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" t="s">
         <v>116</v>
-      </c>
-      <c r="F33" t="s">
-        <v>117</v>
       </c>
       <c r="G33" t="s">
         <v>18</v>
@@ -2321,19 +2315,19 @@
         <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C34" t="s">
+        <v>117</v>
+      </c>
+      <c r="D34" t="s">
         <v>118</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="F34" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G34" t="s">
         <v>18</v>
@@ -2359,10 +2353,10 @@
         <v>37</v>
       </c>
       <c r="D35" t="s">
+        <v>120</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="F35" t="s">
         <v>77</v>
@@ -2397,10 +2391,10 @@
         <v>56</v>
       </c>
       <c r="D36" t="s">
+        <v>122</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="F36" t="s">
         <v>59</v>
@@ -2429,19 +2423,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C37" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D37" t="s">
+        <v>124</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="F37" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G37" t="s">
         <v>18</v>
@@ -2473,13 +2467,13 @@
         <v>14</v>
       </c>
       <c r="D38" t="s">
+        <v>126</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="F38" t="s">
         <v>128</v>
-      </c>
-      <c r="F38" t="s">
-        <v>129</v>
       </c>
       <c r="I38" t="s">
         <v>19</v>
@@ -2505,13 +2499,13 @@
         <v>26</v>
       </c>
       <c r="D39" t="s">
+        <v>129</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="F39" t="s">
         <v>131</v>
-      </c>
-      <c r="F39" t="s">
-        <v>132</v>
       </c>
       <c r="G39" t="s">
         <v>18</v>
@@ -2540,7 +2534,7 @@
         <v>71</v>
       </c>
       <c r="D40" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F40" t="s">
         <v>73</v>
@@ -2575,10 +2569,10 @@
         <v>21</v>
       </c>
       <c r="D41" t="s">
+        <v>133</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="F41" t="s">
         <v>86</v>
@@ -2607,10 +2601,10 @@
         <v>21</v>
       </c>
       <c r="D42" t="s">
+        <v>133</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="F42" t="s">
         <v>86</v>
@@ -2639,10 +2633,10 @@
         <v>47</v>
       </c>
       <c r="D43" t="s">
+        <v>135</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="F43" t="s">
         <v>86</v>
@@ -2703,13 +2697,13 @@
         <v>14</v>
       </c>
       <c r="D45" t="s">
+        <v>137</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="F45" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I45" t="s">
         <v>19</v>
@@ -2735,13 +2729,13 @@
         <v>14</v>
       </c>
       <c r="D46" t="s">
+        <v>137</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="F46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I46" t="s">
         <v>19</v>
@@ -2761,19 +2755,19 @@
         <v>36</v>
       </c>
       <c r="B47" t="s">
+        <v>112</v>
+      </c>
+      <c r="C47" t="s">
         <v>113</v>
       </c>
-      <c r="C47" t="s">
-        <v>114</v>
-      </c>
       <c r="D47" t="s">
+        <v>139</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="F47" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G47" t="s">
         <v>18</v>
@@ -2802,17 +2796,20 @@
         <v>31</v>
       </c>
       <c r="D48" t="s">
+        <v>141</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E48" s="1">
-        <v>10</v>
-      </c>
       <c r="F48" t="s">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="G48" t="s">
         <v>18</v>
       </c>
+      <c r="H48" t="s">
+        <v>144</v>
+      </c>
       <c r="I48" t="s">
         <v>34</v>
       </c>
@@ -2820,7 +2817,7 @@
         <v>46331.25</v>
       </c>
       <c r="K48" s="2">
-        <v>46331.666666666664</v>
+        <v>46331.75</v>
       </c>
       <c r="L48" t="s">
         <v>35</v>
@@ -2837,20 +2834,17 @@
         <v>31</v>
       </c>
       <c r="D49" t="s">
-        <v>143</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
+      </c>
+      <c r="E49" s="1">
+        <v>10</v>
       </c>
       <c r="F49" t="s">
-        <v>145</v>
+        <v>33</v>
       </c>
       <c r="G49" t="s">
         <v>18</v>
       </c>
-      <c r="H49" t="s">
-        <v>146</v>
-      </c>
       <c r="I49" t="s">
         <v>34</v>
       </c>
@@ -2858,7 +2852,7 @@
         <v>46331.25</v>
       </c>
       <c r="K49" s="2">
-        <v>46331.75</v>
+        <v>46331.666666666664</v>
       </c>
       <c r="L49" t="s">
         <v>35</v>
@@ -2869,19 +2863,19 @@
         <v>36</v>
       </c>
       <c r="B50" t="s">
+        <v>112</v>
+      </c>
+      <c r="C50" t="s">
         <v>113</v>
       </c>
-      <c r="C50" t="s">
-        <v>114</v>
-      </c>
       <c r="D50" t="s">
+        <v>146</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="F50" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G50" t="s">
         <v>18</v>
@@ -2910,13 +2904,13 @@
         <v>47</v>
       </c>
       <c r="D51" t="s">
+        <v>148</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="F51" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I51" t="s">
         <v>19</v>
@@ -2942,13 +2936,13 @@
         <v>47</v>
       </c>
       <c r="D52" t="s">
+        <v>148</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="F52" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I52" t="s">
         <v>19</v>
@@ -2974,7 +2968,7 @@
         <v>31</v>
       </c>
       <c r="D53" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E53" s="1">
         <v>10</v>
@@ -3009,19 +3003,19 @@
         <v>31</v>
       </c>
       <c r="D54" t="s">
+        <v>141</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F54" t="s">
         <v>143</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F54" t="s">
-        <v>145</v>
       </c>
       <c r="G54" t="s">
         <v>18</v>
       </c>
       <c r="H54" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I54" t="s">
         <v>34</v>
@@ -3044,16 +3038,16 @@
         <v>37</v>
       </c>
       <c r="C55" t="s">
+        <v>150</v>
+      </c>
+      <c r="D55" t="s">
         <v>151</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="F55" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I55" t="s">
         <v>19</v>
@@ -3076,10 +3070,10 @@
         <v>55</v>
       </c>
       <c r="D56" t="s">
+        <v>153</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="F56" t="s">
         <v>59</v>
@@ -3108,10 +3102,10 @@
         <v>55</v>
       </c>
       <c r="D57" t="s">
+        <v>153</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="F57" t="s">
         <v>59</v>
@@ -3143,13 +3137,13 @@
         <v>31</v>
       </c>
       <c r="D58" t="s">
+        <v>155</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="F58" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G58" t="s">
         <v>18</v>
@@ -3169,25 +3163,25 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="C59" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="D59" t="s">
-        <v>158</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F59" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="G59" t="s">
-        <v>18</v>
+        <v>73</v>
+      </c>
+      <c r="H59" t="s">
+        <v>74</v>
       </c>
       <c r="I59" t="s">
         <v>19</v>
@@ -3196,7 +3190,7 @@
         <v>46332.291666666664</v>
       </c>
       <c r="K59" s="2">
-        <v>46334.166666666664</v>
+        <v>46333.125</v>
       </c>
       <c r="L59" t="s">
         <v>24</v>
@@ -3233,25 +3227,25 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B61" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="C61" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="D61" t="s">
-        <v>160</v>
+        <v>158</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F61" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="G61" t="s">
-        <v>73</v>
-      </c>
-      <c r="H61" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="I61" t="s">
         <v>19</v>
@@ -3260,7 +3254,7 @@
         <v>46332.291666666664</v>
       </c>
       <c r="K61" s="2">
-        <v>46333.125</v>
+        <v>46334.166666666664</v>
       </c>
       <c r="L61" t="s">
         <v>24</v>
@@ -3271,10 +3265,10 @@
         <v>36</v>
       </c>
       <c r="B62" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C62" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D62" t="s">
         <v>158</v>
@@ -3283,7 +3277,7 @@
         <v>159</v>
       </c>
       <c r="F62" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G62" t="s">
         <v>18</v>
@@ -3309,7 +3303,7 @@
         <v>37</v>
       </c>
       <c r="D63" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F63" t="s">
         <v>77</v>
@@ -3335,7 +3329,7 @@
         <v>37</v>
       </c>
       <c r="D64" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F64" t="s">
         <v>77</v>
@@ -3378,9 +3372,6 @@
       <c r="K65" s="2">
         <v>46333.041666666664</v>
       </c>
-      <c r="L65" t="s">
-        <v>100</v>
-      </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
@@ -3393,13 +3384,13 @@
         <v>31</v>
       </c>
       <c r="D66" t="s">
+        <v>155</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="F66" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G66" t="s">
         <v>18</v>
@@ -3425,16 +3416,16 @@
         <v>37</v>
       </c>
       <c r="C67" t="s">
+        <v>161</v>
+      </c>
+      <c r="D67" t="s">
         <v>162</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="F67" t="s">
         <v>164</v>
-      </c>
-      <c r="F67" t="s">
-        <v>165</v>
       </c>
       <c r="I67" t="s">
         <v>19</v>
@@ -3460,7 +3451,7 @@
         <v>38</v>
       </c>
       <c r="D68" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E68" s="1">
         <v>102</v>
@@ -3492,13 +3483,13 @@
         <v>31</v>
       </c>
       <c r="D69" t="s">
+        <v>166</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="F69" t="s">
         <v>168</v>
-      </c>
-      <c r="F69" t="s">
-        <v>169</v>
       </c>
       <c r="G69" t="s">
         <v>18</v>
@@ -3527,7 +3518,7 @@
         <v>43</v>
       </c>
       <c r="D70" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E70" s="1">
         <v>94</v>
@@ -3559,10 +3550,10 @@
         <v>31</v>
       </c>
       <c r="D71" t="s">
+        <v>170</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="F71" t="s">
         <v>86</v>
@@ -3594,7 +3585,7 @@
         <v>31</v>
       </c>
       <c r="D72" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E72" s="1">
         <v>11</v>
@@ -3629,10 +3620,10 @@
         <v>31</v>
       </c>
       <c r="D73" t="s">
+        <v>170</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="F73" t="s">
         <v>86</v>
@@ -3664,10 +3655,10 @@
         <v>26</v>
       </c>
       <c r="D74" t="s">
+        <v>173</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="F74" t="s">
         <v>86</v>
@@ -3696,7 +3687,7 @@
         <v>31</v>
       </c>
       <c r="D75" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -3731,7 +3722,7 @@
         <v>31</v>
       </c>
       <c r="D76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -3766,10 +3757,10 @@
         <v>56</v>
       </c>
       <c r="D77" t="s">
+        <v>176</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>178</v>
       </c>
       <c r="F77" t="s">
         <v>59</v>
@@ -3789,19 +3780,22 @@
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B78" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="C78" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="D78" t="s">
-        <v>92</v>
+        <v>178</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>179</v>
       </c>
       <c r="F78" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="I78" t="s">
         <v>19</v>
@@ -3810,7 +3804,7 @@
         <v>46337.333333333336</v>
       </c>
       <c r="K78" s="2">
-        <v>46337.833333333336</v>
+        <v>46339.333333333336</v>
       </c>
       <c r="L78" t="s">
         <v>24</v>
@@ -3818,22 +3812,19 @@
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="C79" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="D79" t="s">
-        <v>179</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>180</v>
+        <v>92</v>
       </c>
       <c r="F79" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="I79" t="s">
         <v>19</v>
@@ -3842,7 +3833,7 @@
         <v>46337.333333333336</v>
       </c>
       <c r="K79" s="2">
-        <v>46339.333333333336</v>
+        <v>46337.833333333336</v>
       </c>
       <c r="L79" t="s">
         <v>24</v>
@@ -3888,10 +3879,10 @@
         <v>31</v>
       </c>
       <c r="D81" t="s">
+        <v>180</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>182</v>
       </c>
       <c r="F81" t="s">
         <v>86</v>
@@ -3920,13 +3911,13 @@
         <v>37</v>
       </c>
       <c r="C82" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D82" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F82" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I82" t="s">
         <v>19</v>
@@ -3946,19 +3937,19 @@
         <v>36</v>
       </c>
       <c r="B83" t="s">
+        <v>112</v>
+      </c>
+      <c r="C83" t="s">
         <v>113</v>
       </c>
-      <c r="C83" t="s">
-        <v>114</v>
-      </c>
       <c r="D83" t="s">
+        <v>183</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E83" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="F83" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I83" t="s">
         <v>19</v>
@@ -3984,10 +3975,10 @@
         <v>47</v>
       </c>
       <c r="D84" t="s">
+        <v>185</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>187</v>
       </c>
       <c r="F84" t="s">
         <v>23</v>
@@ -4016,10 +4007,10 @@
         <v>47</v>
       </c>
       <c r="D85" t="s">
+        <v>185</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>187</v>
       </c>
       <c r="F85" t="s">
         <v>23</v>
@@ -4048,13 +4039,13 @@
         <v>38</v>
       </c>
       <c r="D86" t="s">
+        <v>187</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E86" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="F86" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I86" t="s">
         <v>19</v>
@@ -4077,16 +4068,16 @@
         <v>37</v>
       </c>
       <c r="C87" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D87" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E87" s="1">
         <v>145</v>
       </c>
       <c r="F87" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I87" t="s">
         <v>19</v>
@@ -4109,16 +4100,16 @@
         <v>37</v>
       </c>
       <c r="C88" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D88" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E88" s="1">
         <v>145</v>
       </c>
       <c r="F88" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I88" t="s">
         <v>19</v>
@@ -4158,9 +4149,6 @@
       <c r="K89" s="2">
         <v>46340.041666666664</v>
       </c>
-      <c r="L89" t="s">
-        <v>100</v>
-      </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
@@ -4173,7 +4161,7 @@
         <v>71</v>
       </c>
       <c r="D90" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F90" t="s">
         <v>73</v>
@@ -4231,19 +4219,19 @@
         <v>31</v>
       </c>
       <c r="D92" t="s">
+        <v>191</v>
+      </c>
+      <c r="E92" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E92" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="F92" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G92" t="s">
         <v>18</v>
       </c>
       <c r="H92" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I92" t="s">
         <v>34</v>
@@ -4263,16 +4251,16 @@
         <v>36</v>
       </c>
       <c r="B93" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C93" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D93" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F93" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I93" t="s">
         <v>19</v>
@@ -4298,7 +4286,7 @@
         <v>43</v>
       </c>
       <c r="D94" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E94" s="1">
         <v>57</v>
@@ -4330,13 +4318,13 @@
         <v>26</v>
       </c>
       <c r="D95" t="s">
+        <v>196</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E95" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="F95" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I95" t="s">
         <v>19</v>
@@ -4362,10 +4350,10 @@
         <v>31</v>
       </c>
       <c r="D96" t="s">
+        <v>198</v>
+      </c>
+      <c r="E96" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="F96" t="s">
         <v>86</v>
@@ -4394,10 +4382,10 @@
         <v>55</v>
       </c>
       <c r="D97" t="s">
+        <v>200</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="F97" t="s">
         <v>59</v>
@@ -4426,10 +4414,10 @@
         <v>31</v>
       </c>
       <c r="D98" t="s">
+        <v>198</v>
+      </c>
+      <c r="E98" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="F98" t="s">
         <v>86</v>
@@ -4455,16 +4443,16 @@
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C99" t="s">
         <v>31</v>
       </c>
       <c r="D99" t="s">
+        <v>202</v>
+      </c>
+      <c r="E99" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="F99" t="s">
         <v>86</v>
@@ -4472,9 +4460,6 @@
       <c r="G99" t="s">
         <v>18</v>
       </c>
-      <c r="H99" t="s">
-        <v>74</v>
-      </c>
       <c r="I99" t="s">
         <v>34</v>
       </c>
@@ -4493,16 +4478,16 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="C100" t="s">
         <v>31</v>
       </c>
       <c r="D100" t="s">
+        <v>204</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="F100" t="s">
         <v>86</v>
@@ -4510,6 +4495,9 @@
       <c r="G100" t="s">
         <v>18</v>
       </c>
+      <c r="H100" t="s">
+        <v>74</v>
+      </c>
       <c r="I100" t="s">
         <v>34</v>
       </c>
@@ -4534,13 +4522,13 @@
         <v>14</v>
       </c>
       <c r="D101" t="s">
+        <v>206</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="F101" t="s">
         <v>208</v>
-      </c>
-      <c r="F101" t="s">
-        <v>209</v>
       </c>
       <c r="I101" t="s">
         <v>19</v>
@@ -4566,13 +4554,13 @@
         <v>14</v>
       </c>
       <c r="D102" t="s">
+        <v>209</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E102" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="F102" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I102" t="s">
         <v>19</v>
@@ -4598,10 +4586,10 @@
         <v>31</v>
       </c>
       <c r="D103" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F103" t="s">
         <v>86</v>
@@ -4633,10 +4621,10 @@
         <v>56</v>
       </c>
       <c r="D104" t="s">
+        <v>211</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="F104" t="s">
         <v>59</v>
@@ -4665,10 +4653,10 @@
         <v>56</v>
       </c>
       <c r="D105" t="s">
+        <v>213</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>215</v>
       </c>
       <c r="F105" t="s">
         <v>59</v>
@@ -4755,20 +4743,17 @@
         <v>31</v>
       </c>
       <c r="D108" t="s">
+        <v>215</v>
+      </c>
+      <c r="E108" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="E108" s="1">
-        <v>89</v>
-      </c>
       <c r="F108" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="G108" t="s">
         <v>18</v>
       </c>
-      <c r="H108" t="s">
-        <v>217</v>
-      </c>
       <c r="I108" t="s">
         <v>34</v>
       </c>
@@ -4793,16 +4778,19 @@
         <v>31</v>
       </c>
       <c r="D109" t="s">
-        <v>218</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
+      </c>
+      <c r="E109" s="1">
+        <v>89</v>
       </c>
       <c r="F109" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="G109" t="s">
         <v>18</v>
+      </c>
+      <c r="H109" t="s">
+        <v>218</v>
       </c>
       <c r="I109" t="s">
         <v>34</v>
@@ -4822,19 +4810,19 @@
         <v>36</v>
       </c>
       <c r="B110" t="s">
+        <v>112</v>
+      </c>
+      <c r="C110" t="s">
         <v>113</v>
       </c>
-      <c r="C110" t="s">
-        <v>114</v>
-      </c>
       <c r="D110" t="s">
+        <v>219</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E110" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="F110" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I110" t="s">
         <v>19</v>
@@ -4860,10 +4848,10 @@
         <v>21</v>
       </c>
       <c r="D111" t="s">
+        <v>221</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>223</v>
       </c>
       <c r="F111" t="s">
         <v>23</v>
@@ -4892,10 +4880,10 @@
         <v>21</v>
       </c>
       <c r="D112" t="s">
+        <v>221</v>
+      </c>
+      <c r="E112" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>223</v>
       </c>
       <c r="F112" t="s">
         <v>23</v>
@@ -4921,16 +4909,16 @@
         <v>37</v>
       </c>
       <c r="C113" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D113" t="s">
+        <v>223</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="E113" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="F113" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I113" t="s">
         <v>19</v>
@@ -4998,9 +4986,6 @@
       </c>
       <c r="K115" s="2">
         <v>46347.041666666664</v>
-      </c>
-      <c r="L115" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="116" spans="1:12">
@@ -5011,16 +4996,16 @@
         <v>37</v>
       </c>
       <c r="C116" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D116" t="s">
+        <v>225</v>
+      </c>
+      <c r="E116" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="E116" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="F116" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I116" t="s">
         <v>19</v>
@@ -5043,16 +5028,16 @@
         <v>37</v>
       </c>
       <c r="C117" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D117" t="s">
+        <v>225</v>
+      </c>
+      <c r="E117" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="E117" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="F117" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I117" t="s">
         <v>19</v>
@@ -5076,20 +5061,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
-  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
-</scriptIds>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -5098,7 +5069,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -5236,18 +5207,32 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
+  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
+</scriptIds>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
 </file>
--- a/data/vessels/2026-10-25.xlsx
+++ b/data/vessels/2026-10-25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="456725" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94C83293-58A5-4D83-915F-57E041F4C8A2}"/>
+  <xr:revisionPtr revIDLastSave="457474" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A77E1DA0-2279-459D-8D04-C064BDF2B9E5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -170,6 +170,15 @@
     <t>COSCO SHIPPING LINES</t>
   </si>
   <si>
+    <t>PN1</t>
+  </si>
+  <si>
+    <t>YM PLUM</t>
+  </si>
+  <si>
+    <t>198E</t>
+  </si>
+  <si>
     <t>CPNW</t>
   </si>
   <si>
@@ -182,15 +191,6 @@
     <t>CMA CGM</t>
   </si>
   <si>
-    <t>PN1</t>
-  </si>
-  <si>
-    <t>YM PLUM</t>
-  </si>
-  <si>
-    <t>198E</t>
-  </si>
-  <si>
     <t>T7</t>
   </si>
   <si>
@@ -302,6 +302,12 @@
     <t>ONE</t>
   </si>
   <si>
+    <t>ONE DURBAN</t>
+  </si>
+  <si>
+    <t>PN32639E</t>
+  </si>
+  <si>
     <t>Oceania</t>
   </si>
   <si>
@@ -311,12 +317,6 @@
     <t>0Y1N2/0T1N3</t>
   </si>
   <si>
-    <t>ONE DURBAN</t>
-  </si>
-  <si>
-    <t>PN32639E</t>
-  </si>
-  <si>
     <t>MATSON ANCHORAGE</t>
   </si>
   <si>
@@ -512,15 +512,15 @@
     <t>KW665</t>
   </si>
   <si>
+    <t>MSC YUKTA X</t>
+  </si>
+  <si>
+    <t>UK644R</t>
+  </si>
+  <si>
     <t>MAUNAWILI</t>
   </si>
   <si>
-    <t>MSC YUKTA X</t>
-  </si>
-  <si>
-    <t>UK644R</t>
-  </si>
-  <si>
     <t>SM MUMBAI</t>
   </si>
   <si>
@@ -686,16 +686,16 @@
     <t>499-144E</t>
   </si>
   <si>
+    <t>GLOVIS SUMMIT</t>
+  </si>
+  <si>
+    <t>APS Stevedoring</t>
+  </si>
+  <si>
     <t>BERGAMOT ACE</t>
   </si>
   <si>
     <t>159A</t>
-  </si>
-  <si>
-    <t>GLOVIS SUMMIT</t>
-  </si>
-  <si>
-    <t>APS Stevedoring</t>
   </si>
   <si>
     <t>MSC ELISABETTA</t>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
         <v>43</v>
@@ -1411,10 +1411,10 @@
         <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="I8" t="s">
         <v>19</v>
@@ -1423,7 +1423,7 @@
         <v>46321.25</v>
       </c>
       <c r="K8" s="2">
-        <v>46322.75</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L8" t="s">
         <v>24</v>
@@ -1431,25 +1431,25 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" t="s">
         <v>47</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" t="s">
         <v>49</v>
       </c>
-      <c r="F9" t="s">
-        <v>23</v>
-      </c>
       <c r="G9" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I9" t="s">
         <v>19</v>
@@ -1458,7 +1458,7 @@
         <v>46321.25</v>
       </c>
       <c r="K9" s="2">
-        <v>46323.166666666664</v>
+        <v>46322.75</v>
       </c>
       <c r="L9" t="s">
         <v>24</v>
@@ -1790,29 +1790,26 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" t="s">
         <v>87</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="G19" t="s">
         <v>18</v>
       </c>
-      <c r="H19" t="s">
-        <v>74</v>
-      </c>
       <c r="I19" t="s">
         <v>19</v>
       </c>
@@ -1820,7 +1817,7 @@
         <v>46324.25</v>
       </c>
       <c r="K19" s="2">
-        <v>46325.166666666664</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="L19" t="s">
         <v>24</v>
@@ -1828,13 +1825,13 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s">
         <v>90</v>
@@ -1843,11 +1840,14 @@
         <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="G20" t="s">
         <v>18</v>
       </c>
+      <c r="H20" t="s">
+        <v>74</v>
+      </c>
       <c r="I20" t="s">
         <v>19</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>46324.25</v>
       </c>
       <c r="K20" s="2">
-        <v>46326.166666666664</v>
+        <v>46325.166666666664</v>
       </c>
       <c r="L20" t="s">
         <v>24</v>
@@ -2178,7 +2178,7 @@
         <v>37</v>
       </c>
       <c r="C30" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D30" t="s">
         <v>107</v>
@@ -2187,7 +2187,7 @@
         <v>108</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G30" t="s">
         <v>18</v>
@@ -2630,7 +2630,7 @@
         <v>25</v>
       </c>
       <c r="C43" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D43" t="s">
         <v>135</v>
@@ -2901,7 +2901,7 @@
         <v>25</v>
       </c>
       <c r="C51" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D51" t="s">
         <v>148</v>
@@ -2933,7 +2933,7 @@
         <v>25</v>
       </c>
       <c r="C52" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D52" t="s">
         <v>148</v>
@@ -3169,20 +3169,14 @@
         <v>70</v>
       </c>
       <c r="C59" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="D59" t="s">
-        <v>157</v>
+        <v>72</v>
       </c>
       <c r="F59" t="s">
         <v>73</v>
       </c>
-      <c r="G59" t="s">
-        <v>73</v>
-      </c>
-      <c r="H59" t="s">
-        <v>74</v>
-      </c>
       <c r="I59" t="s">
         <v>19</v>
       </c>
@@ -3190,7 +3184,7 @@
         <v>46332.291666666664</v>
       </c>
       <c r="K59" s="2">
-        <v>46333.125</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L59" t="s">
         <v>24</v>
@@ -3198,19 +3192,25 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B60" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="C60" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="D60" t="s">
-        <v>72</v>
+        <v>157</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>158</v>
       </c>
       <c r="F60" t="s">
-        <v>73</v>
+        <v>116</v>
+      </c>
+      <c r="G60" t="s">
+        <v>18</v>
       </c>
       <c r="I60" t="s">
         <v>19</v>
@@ -3219,7 +3219,7 @@
         <v>46332.291666666664</v>
       </c>
       <c r="K60" s="2">
-        <v>46332.791666666664</v>
+        <v>46334.166666666664</v>
       </c>
       <c r="L60" t="s">
         <v>24</v>
@@ -3236,10 +3236,10 @@
         <v>117</v>
       </c>
       <c r="D61" t="s">
+        <v>157</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="F61" t="s">
         <v>116</v>
@@ -3262,25 +3262,25 @@
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="C62" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="D62" t="s">
-        <v>158</v>
-      </c>
-      <c r="E62" s="1" t="s">
         <v>159</v>
       </c>
       <c r="F62" t="s">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="G62" t="s">
-        <v>18</v>
+        <v>73</v>
+      </c>
+      <c r="H62" t="s">
+        <v>74</v>
       </c>
       <c r="I62" t="s">
         <v>19</v>
@@ -3289,7 +3289,7 @@
         <v>46332.291666666664</v>
       </c>
       <c r="K62" s="2">
-        <v>46334.166666666664</v>
+        <v>46333.125</v>
       </c>
       <c r="L62" t="s">
         <v>24</v>
@@ -3515,7 +3515,7 @@
         <v>37</v>
       </c>
       <c r="C70" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D70" t="s">
         <v>169</v>
@@ -3524,7 +3524,7 @@
         <v>94</v>
       </c>
       <c r="F70" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I70" t="s">
         <v>19</v>
@@ -3972,7 +3972,7 @@
         <v>25</v>
       </c>
       <c r="C84" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D84" t="s">
         <v>185</v>
@@ -4004,7 +4004,7 @@
         <v>25</v>
       </c>
       <c r="C85" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D85" t="s">
         <v>185</v>
@@ -4283,7 +4283,7 @@
         <v>37</v>
       </c>
       <c r="C94" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D94" t="s">
         <v>195</v>
@@ -4292,7 +4292,7 @@
         <v>57</v>
       </c>
       <c r="F94" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I94" t="s">
         <v>19</v>
@@ -4745,15 +4745,18 @@
       <c r="D108" t="s">
         <v>215</v>
       </c>
-      <c r="E108" s="1" t="s">
-        <v>216</v>
+      <c r="E108" s="1">
+        <v>89</v>
       </c>
       <c r="F108" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="G108" t="s">
         <v>18</v>
       </c>
+      <c r="H108" t="s">
+        <v>216</v>
+      </c>
       <c r="I108" t="s">
         <v>34</v>
       </c>
@@ -4780,17 +4783,14 @@
       <c r="D109" t="s">
         <v>217</v>
       </c>
-      <c r="E109" s="1">
-        <v>89</v>
+      <c r="E109" s="1" t="s">
+        <v>218</v>
       </c>
       <c r="F109" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="G109" t="s">
         <v>18</v>
-      </c>
-      <c r="H109" t="s">
-        <v>218</v>
       </c>
       <c r="I109" t="s">
         <v>34</v>
@@ -4996,7 +4996,7 @@
         <v>37</v>
       </c>
       <c r="C116" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D116" t="s">
         <v>225</v>
@@ -5028,7 +5028,7 @@
         <v>37</v>
       </c>
       <c r="C117" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D117" t="s">
         <v>225</v>
@@ -5061,15 +5061,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -5207,13 +5198,13 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
   <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
   <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
@@ -5221,18 +5212,27 @@
 </scriptIds>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>